--- a/Sunrise_Clock_Parts.xlsx
+++ b/Sunrise_Clock_Parts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asher\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35999A17-B4D0-4AE3-94BA-9A056BA8036E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA4B1CA-8D93-45C8-B9B2-20E03FA47C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,12 +60,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="134">
   <si>
     <t>Sunrise Clock: parts, Amazon vs AliExpress</t>
   </si>
   <si>
-    <t>One clock, every function. Prices checked 2026-10-20 on amazon.com and aliexpress.us (AliExpress: regular price, not the one-time new-shopper deal). Prices change. ESP32 and PLA not included (you have them).</t>
+    <t>One clock, every function. Prices checked 2026-10-20 on amazon.com and aliexpress.us (AliExpress: regular price, not the one-time new-shopper deal). Prices change. ESP32 and PLA not included (you have them). AliExpress 'Choice' items ship together, free once they total about $10; other AliExpress sellers each charge shipping.</t>
   </si>
   <si>
     <t>Part</t>
@@ -236,10 +236,13 @@
     <t>4.4★</t>
   </si>
   <si>
-    <t>4.9★, 900+ sold</t>
-  </si>
-  <si>
-    <t>DS3231SN</t>
+    <t>1 pc, Choice</t>
+  </si>
+  <si>
+    <t>4.8★, 4,000+ sold, Choice</t>
+  </si>
+  <si>
+    <t>DS3231SN, blue board with coin-cell holder</t>
   </si>
   <si>
     <t>DS3231M chips are less accurate but still work. Remove the charging resistor for a CR2032.</t>
@@ -287,13 +290,16 @@
     <t>no reviews yet</t>
   </si>
   <si>
-    <t>dual 5.1K board</t>
-  </si>
-  <si>
-    <t>4.8★, 2,000+ sold</t>
-  </si>
-  <si>
-    <t>AliExpress listing is the proven one here</t>
+    <t>Type-C board, CC1/CC2 5.1K, Choice</t>
+  </si>
+  <si>
+    <t>5★, 347 sold, Choice</t>
+  </si>
+  <si>
+    <t>with 5.1K resistors</t>
+  </si>
+  <si>
+    <t>AliExpress listing has the better track record here</t>
   </si>
   <si>
     <t>HLK-LD2410C sleep radar</t>
@@ -305,7 +311,10 @@
     <t>4.6★, 9 reviews</t>
   </si>
   <si>
-    <t>571 sold</t>
+    <t>4.8★, 5,000+ sold, Choice</t>
+  </si>
+  <si>
+    <t>LD2410C (not B or 2420)</t>
   </si>
   <si>
     <t>Same Hi-Link module. Pocket is 22 × 16 mm: measure yours.</t>
@@ -392,7 +401,13 @@
     <t>HiLetgo 3 pcs</t>
   </si>
   <si>
-    <t>516 sold</t>
+    <t>GY-302, Choice</t>
+  </si>
+  <si>
+    <t>5★, 414 sold, Choice</t>
+  </si>
+  <si>
+    <t>GY-302</t>
   </si>
   <si>
     <t>Only needed for auto-dim</t>
@@ -440,7 +455,7 @@
     <t>Yellow cells (My pick): choose Amazon, AliExpress or None from the dropdown. My price and its total update.</t>
   </si>
   <si>
-    <t>Blue numbers are prices typed in from the listings on 2026-10-20; black numbers are formulas.</t>
+    <t>Blue numbers are prices typed in from the listings on 2026-10-20 (Choice swaps 2026-10-21); black numbers are formulas.</t>
   </si>
   <si>
     <t>Click a listing name to open it. On AliExpress, choose the option in the 'AliExpress option to pick' column.</t>
@@ -1261,7 +1276,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="28" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="42" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>55</v>
       </c>
@@ -1278,35 +1293,35 @@
         <v>57</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G11" s="5">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J11" s="6">
         <f t="shared" si="0"/>
-        <v>5.16</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="6">
         <f t="shared" si="1"/>
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -1321,13 +1336,13 @@
         <v>43</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12" s="5">
         <v>1.48</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="6">
@@ -1342,36 +1357,36 @@
         <v>1.48</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="28" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" s="5">
         <v>7.99</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" s="5">
         <v>4.4000000000000004</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J13" s="6">
         <f t="shared" si="0"/>
@@ -1385,100 +1400,104 @@
         <v>7.99</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="28" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" s="5">
         <v>8.9</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14" s="5">
-        <v>0.41</v>
+        <v>2.86</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I14" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="J14" s="6">
         <f t="shared" si="0"/>
-        <v>8.49</v>
+        <v>6.0400000000000009</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L14" s="6">
         <f t="shared" si="1"/>
-        <v>0.41</v>
+        <v>2.86</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="28" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D15" s="5">
         <v>13.99</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G15" s="5">
-        <v>4.1900000000000004</v>
+        <v>5.91</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="I15" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="J15" s="6">
         <f t="shared" si="0"/>
-        <v>9.8000000000000007</v>
+        <v>8.08</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L15" s="6">
         <f t="shared" si="1"/>
-        <v>4.1900000000000004</v>
+        <v>5.91</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D16" s="5">
         <v>3.99</v>
@@ -1487,14 +1506,14 @@
         <v>38</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G16" s="5">
         <v>3.32</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J16" s="6">
         <f t="shared" si="0"/>
@@ -1508,18 +1527,18 @@
         <v>3.32</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B17" s="3">
         <v>1</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D17" s="5">
         <v>13.99</v>
@@ -1534,10 +1553,10 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J17" s="6">
         <f t="shared" si="0"/>
@@ -1551,18 +1570,18 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D18" s="5">
         <v>5.99</v>
@@ -1571,16 +1590,16 @@
         <v>25</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G18" s="5">
         <v>2.71</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J18" s="6">
         <f t="shared" si="0"/>
@@ -1594,36 +1613,36 @@
         <v>2.71</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B19" s="3">
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D19" s="5">
         <v>8.99</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G19" s="5">
         <v>5.65</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J19" s="6">
         <f t="shared" si="0"/>
@@ -1637,12 +1656,12 @@
         <v>5.65</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -1654,37 +1673,37 @@
       <c r="F20" s="9"/>
       <c r="G20" s="10">
         <f>SUM(G5:G19)</f>
-        <v>50.410000000000004</v>
+        <v>54.89</v>
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
       <c r="J20" s="10">
         <f>SUM(J5:J19)</f>
-        <v>79.140000000000015</v>
+        <v>74.660000000000011</v>
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="10">
         <f>SUM(L5:L19)</f>
-        <v>58.149999999999991</v>
+        <v>62.629999999999995</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="28" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D23" s="5">
         <v>7.49</v>
@@ -1693,33 +1712,35 @@
         <v>43</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="G23" s="5">
-        <v>4.05</v>
+        <v>2.19</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I23" s="3"/>
+        <v>114</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="J23" s="6">
         <f>D23-G23</f>
-        <v>3.4400000000000004</v>
+        <v>5.3000000000000007</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L23" s="6">
         <f>IF(K23="Amazon",D23,IF(K23="AliExpress",G23,0))</f>
-        <v>4.05</v>
+        <v>2.19</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -1731,29 +1752,29 @@
       <c r="F24" s="9"/>
       <c r="G24" s="10">
         <f>G20+SUM(G23:G23)</f>
-        <v>54.46</v>
+        <v>57.08</v>
       </c>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
       <c r="J24" s="10">
         <f>J20+SUM(J23:J23)</f>
-        <v>82.580000000000013</v>
+        <v>79.960000000000008</v>
       </c>
       <c r="K24" s="9"/>
       <c r="L24" s="10">
         <f>L20+SUM(L23:L23)</f>
-        <v>62.199999999999989</v>
+        <v>64.819999999999993</v>
       </c>
       <c r="M24" s="9"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="12" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="28" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -1769,12 +1790,12 @@
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
       <c r="M27" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -1790,12 +1811,12 @@
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
       <c r="M28" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -1811,12 +1832,12 @@
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
       <c r="M29" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="28" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -1832,12 +1853,12 @@
       <c r="K30" s="13"/>
       <c r="L30" s="13"/>
       <c r="M30" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -1853,32 +1874,32 @@
       <c r="K31" s="13"/>
       <c r="L31" s="13"/>
       <c r="M31" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="14" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="15" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="15" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="15" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Sunrise_Clock_Parts.xlsx
+++ b/Sunrise_Clock_Parts.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asher\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA4B1CA-8D93-45C8-B9B2-20E03FA47C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08BD59C-0B72-4114-B13F-53635DDF17EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6400" yWindow="2250" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parts" sheetId="1" r:id="rId1"/>
+    <sheet name="Buying" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">Buying!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Parts!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -60,12 +62,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="154">
   <si>
     <t>Sunrise Clock: parts, Amazon vs AliExpress</t>
   </si>
   <si>
-    <t>One clock, every function. Prices checked 2026-10-20 on amazon.com and aliexpress.us (AliExpress: regular price, not the one-time new-shopper deal). Prices change. ESP32 and PLA not included (you have them). AliExpress 'Choice' items ship together, free once they total about $10; other AliExpress sellers each charge shipping.</t>
+    <t>Total:</t>
+  </si>
+  <si>
+    <t>One clock, every function. Prices checked 2026-10-20 on amazon.com and aliexpress.us (AliExpress: regular price, not the one-time new-shopper deal). Prices change. ESP32 and PLA not included (you have them).</t>
   </si>
   <si>
     <t>Part</t>
@@ -74,6 +79,216 @@
     <t>Qty</t>
   </si>
   <si>
+    <t xml:space="preserve"> listing</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>My pick</t>
+  </si>
+  <si>
+    <t>Option to pick</t>
+  </si>
+  <si>
+    <t>LED strip, WS2812B, 1 m, 10 mm wide</t>
+  </si>
+  <si>
+    <t>ANTVLED 96 LED/m IP30</t>
+  </si>
+  <si>
+    <t>AliExpress</t>
+  </si>
+  <si>
+    <t>White PCB, 1m 96 IP30</t>
+  </si>
+  <si>
+    <t>74AHCT125 level shifter (DIP-14)</t>
+  </si>
+  <si>
+    <t>5 pcs</t>
+  </si>
+  <si>
+    <t>5PCS SN74AHCT125N</t>
+  </si>
+  <si>
+    <t>MAX98357A I2S amplifier</t>
+  </si>
+  <si>
+    <t>1 pc</t>
+  </si>
+  <si>
+    <t>1PCS</t>
+  </si>
+  <si>
+    <t>Speaker, 2" 4 Ω 3 W</t>
+  </si>
+  <si>
+    <t>Gikfun EK1725, 2 pcs</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>2 pcs</t>
+  </si>
+  <si>
+    <t>DS3231 RTC (ZS-042)</t>
+  </si>
+  <si>
+    <t>1 pc, Choice</t>
+  </si>
+  <si>
+    <t>only one option</t>
+  </si>
+  <si>
+    <t>KY-040 rotary encoder</t>
+  </si>
+  <si>
+    <t>1 pc + knob</t>
+  </si>
+  <si>
+    <t>12 mm momentary push buttons</t>
+  </si>
+  <si>
+    <t>Gebildet 5 pcs (pick Flat Head)</t>
+  </si>
+  <si>
+    <t>SS-Momentary-5pcs (Flat Head)</t>
+  </si>
+  <si>
+    <t>USB-C power input, dual 5.1 kΩ</t>
+  </si>
+  <si>
+    <t>Type-C board, CC1/CC2 5.1K, Choice</t>
+  </si>
+  <si>
+    <t>army green (blue board), 1PCS</t>
+  </si>
+  <si>
+    <t>HLK-LD2410C sleep radar</t>
+  </si>
+  <si>
+    <t>1pc</t>
+  </si>
+  <si>
+    <t>Jumper wires, female-female</t>
+  </si>
+  <si>
+    <t>40 pin</t>
+  </si>
+  <si>
+    <t>20CM Female-Female, 1Set-40Pin</t>
+  </si>
+  <si>
+    <t>Protoboards</t>
+  </si>
+  <si>
+    <t>Red 3x7cm, 5PCS</t>
+  </si>
+  <si>
+    <t>M3 heat-set inserts</t>
+  </si>
+  <si>
+    <t>brass inserts</t>
+  </si>
+  <si>
+    <t>M3 (OD 4.5mm) 50pcs, Length 5mm</t>
+  </si>
+  <si>
+    <t>Male header pins</t>
+  </si>
+  <si>
+    <t>11.5mm 10pcs</t>
+  </si>
+  <si>
+    <t>Total (core build)</t>
+  </si>
+  <si>
+    <t>BH1750 light sensor (auto-dim, optional)</t>
+  </si>
+  <si>
+    <t>GY-302, Choice</t>
+  </si>
+  <si>
+    <t>GY-302 1PCS</t>
+  </si>
+  <si>
+    <t>Total with optional parts</t>
+  </si>
+  <si>
+    <t>Same on both sites (not in the totals)</t>
+  </si>
+  <si>
+    <t>Dot Matrix Display</t>
+  </si>
+  <si>
+    <t>most likely buying</t>
+  </si>
+  <si>
+    <t>Dot-matrix clock: Adafruit 0.8" 8x16 LED Matrix FeatherWing kit, white</t>
+  </si>
+  <si>
+    <t>…or the yellow version (cheaper)</t>
+  </si>
+  <si>
+    <t>5 V 3 A USB-C power supply</t>
+  </si>
+  <si>
+    <t>think I can find</t>
+  </si>
+  <si>
+    <t>Fabric: muslin, 1.3 yd</t>
+  </si>
+  <si>
+    <t>can find</t>
+  </si>
+  <si>
+    <t>CR2032 coin cells, 24 pack</t>
+  </si>
+  <si>
+    <t>M3 countersunk screws</t>
+  </si>
+  <si>
+    <t>630 pcs kit</t>
+  </si>
+  <si>
+    <t>kit</t>
+  </si>
+  <si>
+    <t>470 Ω resistor</t>
+  </si>
+  <si>
+    <t>California JOS 100 pcs</t>
+  </si>
+  <si>
+    <t>100 pcs metal film</t>
+  </si>
+  <si>
+    <t>1000 µF 16 V capacitor</t>
+  </si>
+  <si>
+    <t>10 pcs, low ESR</t>
+  </si>
+  <si>
+    <t>DIP electrolytic</t>
+  </si>
+  <si>
+    <t>How to use</t>
+  </si>
+  <si>
+    <t>Yellow cells (My pick): choose Amazon, AliExpress or None from the dropdown. My price and its total update.</t>
+  </si>
+  <si>
+    <t>Blue numbers are prices typed in from the listings on 2026-10-20; black numbers are formulas.</t>
+  </si>
+  <si>
+    <t>Click a listing name to open it. On AliExpress, choose the option in the 'AliExpress option to pick' column.</t>
+  </si>
+  <si>
+    <t>Quality: most are the same boards on both sites. Amazon = fast, free returns, spares. AliExpress = ~60% cheaper, test parts on arrival.</t>
+  </si>
+  <si>
     <t>Amazon listing</t>
   </si>
   <si>
@@ -98,67 +313,205 @@
     <t>Amazon − AliExpress</t>
   </si>
   <si>
-    <t>My pick</t>
-  </si>
-  <si>
     <t>My price</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>LED strip, WS2812B, 1 m, 10 mm wide</t>
-  </si>
-  <si>
     <t>BTF-Lighting 100 LED/m IP30</t>
   </si>
   <si>
     <t>4.6★</t>
   </si>
   <si>
-    <t>ANTVLED 96 LED/m IP30</t>
-  </si>
-  <si>
     <t>4.8★, 5,000+ sold</t>
   </si>
   <si>
     <t>1m 96 IP30</t>
   </si>
   <si>
-    <t>AliExpress</t>
-  </si>
-  <si>
     <t>BTF is a known brand, consistent color. Ali store 94.8% positive. Both strips fit the channels.</t>
   </si>
   <si>
-    <t>74AHCT125 level shifter (DIP-14)</t>
-  </si>
-  <si>
     <t>10 pcs</t>
   </si>
   <si>
     <t>4.7★</t>
   </si>
   <si>
-    <t>5 pcs</t>
-  </si>
-  <si>
     <t>4.9★, 2,000+ sold</t>
   </si>
   <si>
     <t>Cheap chips can be relabeled 74HC parts that won't shift 3.3 V to 5 V. First suspect if the LEDs flicker.</t>
   </si>
   <si>
-    <t>470 Ω resistor</t>
-  </si>
-  <si>
-    <t>California JOS 100 pcs</t>
-  </si>
-  <si>
-    <t>5.0★</t>
-  </si>
-  <si>
-    <t>100 pcs metal film</t>
+    <t>4.5★</t>
+  </si>
+  <si>
+    <t>4.8★, 4,000+ sold</t>
+  </si>
+  <si>
+    <t>Same board design</t>
+  </si>
+  <si>
+    <t>4.3★, 776 reviews</t>
+  </si>
+  <si>
+    <t>SOTAMIA 50 mm, 2 pcs</t>
+  </si>
+  <si>
+    <t>528 sold</t>
+  </si>
+  <si>
+    <t>4 Ohm 3W</t>
+  </si>
+  <si>
+    <t>Gikfun is better proven. Both fit the seat (glue it in).</t>
+  </si>
+  <si>
+    <t>2 pcs + jumper wires</t>
+  </si>
+  <si>
+    <t>4.4★</t>
+  </si>
+  <si>
+    <t>4.8★, 4,000+ sold, Choice</t>
+  </si>
+  <si>
+    <t>DS3231SN, blue board with coin-cell holder</t>
+  </si>
+  <si>
+    <t>DS3231M chips are less accurate but still work. Remove the charging resistor for a CR2032.</t>
+  </si>
+  <si>
+    <t>4.7★, 1,000+ sold</t>
+  </si>
+  <si>
+    <t>Same module, with the pull-ups GPIO34/35 need</t>
+  </si>
+  <si>
+    <t>4.6★, 981 reviews</t>
+  </si>
+  <si>
+    <t>1 pc each, price for 2</t>
+  </si>
+  <si>
+    <t>90 sold</t>
+  </si>
+  <si>
+    <t>Momentary</t>
+  </si>
+  <si>
+    <t>Amazon's are much better reviewed. Weakest AliExpress listing.</t>
+  </si>
+  <si>
+    <t>eleUniverse 2 pcs</t>
+  </si>
+  <si>
+    <t>no reviews yet</t>
+  </si>
+  <si>
+    <t>5★, 347 sold, Choice</t>
+  </si>
+  <si>
+    <t>with 5.1K resistors</t>
+  </si>
+  <si>
+    <t>AliExpress listing has the better track record here</t>
+  </si>
+  <si>
+    <t>AEDIKO 2 pcs</t>
+  </si>
+  <si>
+    <t>4.6★, 9 reviews</t>
+  </si>
+  <si>
+    <t>4.8★, 5,000+ sold, Choice</t>
+  </si>
+  <si>
+    <t>LD2410C (not B or 2420)</t>
+  </si>
+  <si>
+    <t>Same Hi-Link module. Pocket is 22 × 16 mm: measure yours.</t>
+  </si>
+  <si>
+    <t>40 pcs, 20 cm</t>
+  </si>
+  <si>
+    <t>4.8★</t>
+  </si>
+  <si>
+    <t>F-F 20cm</t>
+  </si>
+  <si>
+    <t>Same</t>
+  </si>
+  <si>
+    <t>58 pcs kit + headers</t>
+  </si>
+  <si>
+    <t>560 sold</t>
+  </si>
+  <si>
+    <t>3x7cm</t>
+  </si>
+  <si>
+    <t>Amazon kit includes headers and terminals</t>
+  </si>
+  <si>
+    <t>My price = your mix. Default: AliExpress, except the speaker and buttons from Amazon.</t>
+  </si>
+  <si>
+    <t>Optional</t>
+  </si>
+  <si>
+    <t>HiLetgo 3 pcs</t>
+  </si>
+  <si>
+    <t>5★, 414 sold, Choice</t>
+  </si>
+  <si>
+    <t>GY-302</t>
+  </si>
+  <si>
+    <t>Only needed for auto-dim</t>
+  </si>
+  <si>
+    <t>OPEN-SMART 0.8" Inch 16x8 I2C LED Dot Matrix Display Module 4 Pin Red LED Matrix for Arduino</t>
+  </si>
+  <si>
+    <t>adafruit.com, plus shipping. Neither site had a good match.</t>
+  </si>
+  <si>
+    <t>adafruit.com, plus shipping</t>
+  </si>
+  <si>
+    <t>Free if you have a USB-C phone charger that does 5 V 3 A</t>
+  </si>
+  <si>
+    <t>Free with an old linen shirt or pillowcase. Hold it up to a lamp: it should glow.</t>
+  </si>
+  <si>
+    <t>Free if you have one at home</t>
+  </si>
+  <si>
+    <t>100 pcs, M3 × 5.7 × 4.6</t>
+  </si>
+  <si>
+    <t>54,000+ sold</t>
+  </si>
+  <si>
+    <t>M3 x 5.7 x 4.6</t>
+  </si>
+  <si>
+    <t>Amazon's size is confirmed; on Ali pick M3 × 5.7 × 4.6 if offered</t>
+  </si>
+  <si>
+    <t>4.8★, 1,000+ sold</t>
+  </si>
+  <si>
+    <t>M3</t>
   </si>
   <si>
     <t>550 sold</t>
@@ -170,308 +523,18 @@
     <t>Same part</t>
   </si>
   <si>
-    <t>1000 µF 16 V capacitor</t>
-  </si>
-  <si>
-    <t>10 pcs, low ESR</t>
-  </si>
-  <si>
-    <t>4.8★</t>
-  </si>
-  <si>
-    <t>DIP electrolytic</t>
-  </si>
-  <si>
     <t>16V 1000uF</t>
-  </si>
-  <si>
-    <t>MAX98357A I2S amplifier</t>
-  </si>
-  <si>
-    <t>2 pcs</t>
-  </si>
-  <si>
-    <t>4.5★</t>
-  </si>
-  <si>
-    <t>1 pc</t>
-  </si>
-  <si>
-    <t>4.8★, 4,000+ sold</t>
-  </si>
-  <si>
-    <t>Same board design</t>
-  </si>
-  <si>
-    <t>Speaker, 2" 4 Ω 3 W</t>
-  </si>
-  <si>
-    <t>Gikfun EK1725, 2 pcs</t>
-  </si>
-  <si>
-    <t>4.3★, 776 reviews</t>
-  </si>
-  <si>
-    <t>SOTAMIA 50 mm, 2 pcs</t>
-  </si>
-  <si>
-    <t>528 sold</t>
-  </si>
-  <si>
-    <t>4 Ohm 3W</t>
-  </si>
-  <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Gikfun is better proven. Both fit the seat (glue it in).</t>
-  </si>
-  <si>
-    <t>DS3231 RTC (ZS-042)</t>
-  </si>
-  <si>
-    <t>2 pcs + jumper wires</t>
-  </si>
-  <si>
-    <t>4.4★</t>
-  </si>
-  <si>
-    <t>1 pc, Choice</t>
-  </si>
-  <si>
-    <t>4.8★, 4,000+ sold, Choice</t>
-  </si>
-  <si>
-    <t>DS3231SN, blue board with coin-cell holder</t>
-  </si>
-  <si>
-    <t>DS3231M chips are less accurate but still work. Remove the charging resistor for a CR2032.</t>
-  </si>
-  <si>
-    <t>KY-040 rotary encoder</t>
-  </si>
-  <si>
-    <t>1 pc + knob</t>
-  </si>
-  <si>
-    <t>4.7★, 1,000+ sold</t>
-  </si>
-  <si>
-    <t>Same module, with the pull-ups GPIO34/35 need</t>
-  </si>
-  <si>
-    <t>12 mm momentary push buttons</t>
-  </si>
-  <si>
-    <t>Gebildet 5 pcs (pick Flat Head)</t>
-  </si>
-  <si>
-    <t>4.6★, 981 reviews</t>
-  </si>
-  <si>
-    <t>1 pc each, price for 2</t>
-  </si>
-  <si>
-    <t>90 sold</t>
-  </si>
-  <si>
-    <t>Momentary</t>
-  </si>
-  <si>
-    <t>Amazon's are much better reviewed. Weakest AliExpress listing.</t>
-  </si>
-  <si>
-    <t>USB-C power input, dual 5.1 kΩ</t>
-  </si>
-  <si>
-    <t>eleUniverse 2 pcs</t>
-  </si>
-  <si>
-    <t>no reviews yet</t>
-  </si>
-  <si>
-    <t>Type-C board, CC1/CC2 5.1K, Choice</t>
-  </si>
-  <si>
-    <t>5★, 347 sold, Choice</t>
-  </si>
-  <si>
-    <t>with 5.1K resistors</t>
-  </si>
-  <si>
-    <t>AliExpress listing has the better track record here</t>
-  </si>
-  <si>
-    <t>HLK-LD2410C sleep radar</t>
-  </si>
-  <si>
-    <t>AEDIKO 2 pcs</t>
-  </si>
-  <si>
-    <t>4.6★, 9 reviews</t>
-  </si>
-  <si>
-    <t>4.8★, 5,000+ sold, Choice</t>
-  </si>
-  <si>
-    <t>LD2410C (not B or 2420)</t>
-  </si>
-  <si>
-    <t>Same Hi-Link module. Pocket is 22 × 16 mm: measure yours.</t>
-  </si>
-  <si>
-    <t>Jumper wires, female-female</t>
-  </si>
-  <si>
-    <t>40 pcs, 20 cm</t>
-  </si>
-  <si>
-    <t>40 pin</t>
-  </si>
-  <si>
-    <t>F-F 20cm</t>
-  </si>
-  <si>
-    <t>Same</t>
-  </si>
-  <si>
-    <t>Protoboards</t>
-  </si>
-  <si>
-    <t>58 pcs kit + headers</t>
-  </si>
-  <si>
-    <t>560 sold</t>
-  </si>
-  <si>
-    <t>3x7cm</t>
-  </si>
-  <si>
-    <t>Amazon kit includes headers and terminals</t>
-  </si>
-  <si>
-    <t>M3 heat-set inserts</t>
-  </si>
-  <si>
-    <t>100 pcs, M3 × 5.7 × 4.6</t>
-  </si>
-  <si>
-    <t>brass inserts</t>
-  </si>
-  <si>
-    <t>54,000+ sold</t>
-  </si>
-  <si>
-    <t>M3 x 5.7 x 4.6</t>
-  </si>
-  <si>
-    <t>Amazon's size is confirmed; on Ali pick M3 × 5.7 × 4.6 if offered</t>
-  </si>
-  <si>
-    <t>M3 countersunk screws</t>
-  </si>
-  <si>
-    <t>630 pcs kit</t>
-  </si>
-  <si>
-    <t>4.3★</t>
-  </si>
-  <si>
-    <t>kit</t>
-  </si>
-  <si>
-    <t>4.8★, 1,000+ sold</t>
-  </si>
-  <si>
-    <t>M3</t>
-  </si>
-  <si>
-    <t>Total (core build)</t>
-  </si>
-  <si>
-    <t>My price = your mix. Default: AliExpress, except the speaker and buttons from Amazon.</t>
-  </si>
-  <si>
-    <t>Optional</t>
-  </si>
-  <si>
-    <t>BH1750 light sensor (auto-dim, optional)</t>
-  </si>
-  <si>
-    <t>HiLetgo 3 pcs</t>
-  </si>
-  <si>
-    <t>GY-302, Choice</t>
-  </si>
-  <si>
-    <t>5★, 414 sold, Choice</t>
-  </si>
-  <si>
-    <t>GY-302</t>
-  </si>
-  <si>
-    <t>Only needed for auto-dim</t>
-  </si>
-  <si>
-    <t>Total with optional parts</t>
-  </si>
-  <si>
-    <t>Same on both sites (not in the totals)</t>
-  </si>
-  <si>
-    <t>Dot-matrix clock: Adafruit 0.8" 8x16 LED Matrix FeatherWing kit, white</t>
-  </si>
-  <si>
-    <t>adafruit.com, plus shipping. Neither site had a good match.</t>
-  </si>
-  <si>
-    <t>…or the yellow version (cheaper)</t>
-  </si>
-  <si>
-    <t>adafruit.com, plus shipping</t>
-  </si>
-  <si>
-    <t>5 V 3 A USB-C power supply</t>
-  </si>
-  <si>
-    <t>Free if you have a USB-C phone charger that does 5 V 3 A</t>
-  </si>
-  <si>
-    <t>Fabric: muslin, 1.3 yd</t>
-  </si>
-  <si>
-    <t>Free with an old linen shirt or pillowcase. Hold it up to a lamp: it should glow.</t>
-  </si>
-  <si>
-    <t>CR2032 coin cells, 24 pack</t>
-  </si>
-  <si>
-    <t>Free if you have one at home</t>
-  </si>
-  <si>
-    <t>How to use</t>
-  </si>
-  <si>
-    <t>Yellow cells (My pick): choose Amazon, AliExpress or None from the dropdown. My price and its total update.</t>
-  </si>
-  <si>
-    <t>Blue numbers are prices typed in from the listings on 2026-10-20 (Choice swaps 2026-10-21); black numbers are formulas.</t>
-  </si>
-  <si>
-    <t>Click a listing name to open it. On AliExpress, choose the option in the 'AliExpress option to pick' column.</t>
-  </si>
-  <si>
-    <t>Quality: most are the same boards on both sites. Amazon = fast, free returns, spares. AliExpress = ~60% cheaper, test parts on arrival.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="\$#,##0.00;\(\$#,##0.00\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -535,6 +598,14 @@
       <sz val="9"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -583,10 +654,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -617,13 +689,69 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -939,7 +1067,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -957,831 +1085,738 @@
     <col min="13" max="13" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17">
+        <f>SUM(G5:G7,G9:G10,G12:G15,D8,D11,G19)</f>
+        <v>51.870000000000005</v>
+      </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
+      <c r="A2" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
     </row>
     <row r="4" spans="1:13" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="L4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="28" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="B5" s="3">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="D5" s="5">
         <v>11.99</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G5" s="5">
         <v>4.59</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J5" s="6">
-        <f t="shared" ref="J5:J19" si="0">D5-G5</f>
+        <f t="shared" ref="J5:J15" si="0">D5-G5</f>
         <v>7.4</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L5" s="6">
-        <f t="shared" ref="L5:L19" si="1">IF(K5="Amazon",D5,IF(K5="AliExpress",G5,0))</f>
+        <f t="shared" ref="L5:L15" si="1">IF(K5="Amazon",D5,IF(K5="AliExpress",G5,0))</f>
         <v>4.59</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="28" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="D6" s="5">
         <v>7.99</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G6" s="5">
         <v>2.41</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J6" s="6">
         <f t="shared" si="0"/>
         <v>5.58</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L6" s="6">
         <f t="shared" si="1"/>
         <v>2.41</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D7" s="5">
-        <v>3.99</v>
+        <v>6.88</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G7" s="5">
-        <v>1.84</v>
+        <v>2.34</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>34</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="I7" s="3"/>
       <c r="J7" s="6">
         <f t="shared" si="0"/>
-        <v>2.1500000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L7" s="6">
         <f t="shared" si="1"/>
-        <v>1.84</v>
+        <v>2.34</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D8" s="5">
-        <v>5.99</v>
+        <v>11.49</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="G8" s="5">
-        <v>2.75</v>
+        <v>7.34</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J8" s="6">
         <f t="shared" si="0"/>
-        <v>3.24</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="6">
         <f t="shared" si="1"/>
-        <v>2.75</v>
+        <v>11.49</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="D9" s="5">
-        <v>6.88</v>
+        <v>7.99</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="G9" s="5">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="3"/>
+        <v>104</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="J9" s="6">
         <f t="shared" si="0"/>
-        <v>4.54</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L9" s="6">
         <f t="shared" si="1"/>
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="28" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D10" s="5">
-        <v>11.49</v>
+        <v>9.39</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="G10" s="5">
-        <v>7.34</v>
+        <v>1.48</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>52</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="I10" s="3"/>
       <c r="J10" s="6">
         <f t="shared" si="0"/>
-        <v>4.1500000000000004</v>
+        <v>7.91</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="L10" s="6">
         <f t="shared" si="1"/>
-        <v>11.49</v>
+        <v>1.48</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="42" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="D11" s="5">
         <v>7.99</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="G11" s="5">
-        <v>3.14</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="J11" s="6">
         <f t="shared" si="0"/>
-        <v>4.8499999999999996</v>
+        <v>3.59</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="6">
         <f t="shared" si="1"/>
-        <v>3.14</v>
+        <v>7.99</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D12" s="5">
-        <v>9.39</v>
+        <v>8.9</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="G12" s="5">
-        <v>1.48</v>
+        <v>2.86</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="3"/>
+        <v>116</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="J12" s="6">
         <f t="shared" si="0"/>
-        <v>7.91</v>
+        <v>6.0400000000000009</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L12" s="6">
         <f t="shared" si="1"/>
-        <v>1.48</v>
+        <v>2.86</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="28" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="B13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="D13" s="5">
-        <v>7.99</v>
+        <v>13.99</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="G13" s="5">
-        <v>4.4000000000000004</v>
+        <v>5.91</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="J13" s="6">
         <f t="shared" si="0"/>
-        <v>3.59</v>
+        <v>8.08</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="L13" s="6">
         <f t="shared" si="1"/>
-        <v>7.99</v>
+        <v>5.91</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="28" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="D14" s="5">
-        <v>8.9</v>
+        <v>3.99</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="G14" s="5">
-        <v>2.86</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>77</v>
-      </c>
+        <v>3.32</v>
+      </c>
+      <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="J14" s="6">
         <f t="shared" si="0"/>
-        <v>6.0400000000000009</v>
+        <v>0.67000000000000037</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L14" s="6">
         <f t="shared" si="1"/>
-        <v>2.86</v>
+        <v>3.32</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="28" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="D15" s="5">
         <v>13.99</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G15" s="5">
-        <v>5.91</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="J15" s="6">
         <f t="shared" si="0"/>
-        <v>8.08</v>
+        <v>9.84</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L15" s="6">
         <f t="shared" si="1"/>
-        <v>5.91</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="3">
-        <v>1</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="5">
-        <v>3.99</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="5">
-        <v>3.32</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="J16" s="6">
-        <f t="shared" si="0"/>
-        <v>0.67000000000000037</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="6">
-        <f t="shared" si="1"/>
-        <v>3.32</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="3">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" s="5">
-        <v>13.99</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="5">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="A16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10" t="str">
+        <f ca="1">SUM(D5:D30)</f>
+        <v/>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="10" t="str">
+        <f ca="1">SUM(G5:G30)</f>
+        <v/>
+      </c>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="10" t="str">
+        <f ca="1">SUM(J5:J30)</f>
+        <v/>
+      </c>
+      <c r="K16" s="9"/>
+      <c r="L16" s="10" t="str">
+        <f ca="1">SUM(L5:L30)</f>
+        <v/>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="5">
+        <v>7.49</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="6">
-        <f t="shared" si="0"/>
-        <v>9.84</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="L17" s="6">
-        <f t="shared" si="1"/>
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" s="3">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="5">
-        <v>5.99</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G18" s="5">
-        <v>2.71</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J18" s="6">
-        <f t="shared" si="0"/>
-        <v>3.2800000000000002</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="L18" s="6">
-        <f t="shared" si="1"/>
-        <v>2.71</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="3">
-        <v>1</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" s="5">
-        <v>8.99</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="F19" s="4" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="G19" s="5">
-        <v>5.65</v>
+        <v>2.19</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="J19" s="6">
-        <f t="shared" si="0"/>
-        <v>3.34</v>
+        <f>D19-G19</f>
+        <v>5.3000000000000007</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L19" s="6">
-        <f t="shared" si="1"/>
-        <v>5.65</v>
+        <f>IF(K19="Amazon",D19,IF(K19="AliExpress",G19,0))</f>
+        <v>2.19</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
-      <c r="D20" s="10">
-        <f>SUM(D5:D19)</f>
-        <v>129.54999999999998</v>
+      <c r="D20" s="10" t="str">
+        <f ca="1">D16+SUM(D19:D19)</f>
+        <v/>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
-      <c r="G20" s="10">
-        <f>SUM(G5:G19)</f>
-        <v>54.89</v>
+      <c r="G20" s="10" t="str">
+        <f ca="1">G16+SUM(G19:G19)</f>
+        <v/>
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="10">
-        <f>SUM(J5:J19)</f>
-        <v>74.660000000000011</v>
+      <c r="J20" s="10" t="str">
+        <f ca="1">J16+SUM(J19:J19)</f>
+        <v/>
       </c>
       <c r="K20" s="9"/>
-      <c r="L20" s="10">
-        <f>SUM(L5:L19)</f>
-        <v>62.629999999999995</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>109</v>
-      </c>
+      <c r="L20" s="10" t="str">
+        <f ca="1">L16+SUM(L19:L19)</f>
+        <v/>
+      </c>
+      <c r="M20" s="9"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="28" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B23" s="3">
-        <v>1</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" s="5">
-        <v>7.49</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G23" s="5">
-        <v>2.19</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J23" s="6">
-        <f>D23-G23</f>
-        <v>5.3000000000000007</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="L23" s="6">
-        <f>IF(K23="Amazon",D23,IF(K23="AliExpress",G23,0))</f>
-        <v>2.19</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="10">
-        <f>D20+SUM(D23:D23)</f>
-        <v>137.04</v>
-      </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="10">
-        <f>G20+SUM(G23:G23)</f>
-        <v>57.08</v>
-      </c>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="10">
-        <f>J20+SUM(J23:J23)</f>
-        <v>79.960000000000008</v>
-      </c>
-      <c r="K24" s="9"/>
-      <c r="L24" s="10">
-        <f>L20+SUM(L23:L23)</f>
-        <v>64.819999999999993</v>
-      </c>
-      <c r="M24" s="9"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" s="16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="5">
+        <v>19.95</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="5">
+        <v>11.95</v>
+      </c>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A26" s="12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="28" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="5">
+        <v>9.99</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
       <c r="D27" s="5">
-        <v>19.95</v>
-      </c>
-      <c r="E27" s="13"/>
+        <v>6.99</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>59</v>
+      </c>
       <c r="F27" s="13"/>
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
@@ -1790,19 +1825,21 @@
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
       <c r="M27" s="3" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="5">
-        <v>11.95</v>
-      </c>
-      <c r="E28" s="13"/>
+        <v>7.99</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>59</v>
+      </c>
       <c r="F28" s="13"/>
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
@@ -1811,113 +1848,232 @@
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
       <c r="M28" s="3" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="D29" s="5">
-        <v>9.99</v>
-      </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
+        <v>5.99</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29" s="5">
+        <v>2.71</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J29" s="6">
+        <f>D29-G29</f>
+        <v>3.2800000000000002</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L29" s="6">
+        <f>IF(K29="Amazon",D29,IF(K29="AliExpress",G29,0))</f>
+        <v>2.71</v>
+      </c>
       <c r="M29" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="28" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="D30" s="5">
-        <v>6.99</v>
-      </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
+        <v>8.99</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30" s="5">
+        <v>5.65</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J30" s="6">
+        <f>D30-G30</f>
+        <v>3.34</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L30" s="6">
+        <f>IF(K30="Amazon",D30,IF(K30="AliExpress",G30,0))</f>
+        <v>5.65</v>
+      </c>
       <c r="M30" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
+      <c r="A31" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="D31" s="5">
-        <v>7.99</v>
-      </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
+        <v>3.99</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G31" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J31" s="6">
+        <f>D31-G31</f>
+        <v>2.1500000000000004</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L31" s="6">
+        <f>IF(K31="Amazon",D31,IF(K31="AliExpress",G31,0))</f>
+        <v>1.84</v>
+      </c>
       <c r="M31" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" s="14" t="s">
-        <v>129</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="5">
+        <v>5.99</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G32" s="5">
+        <v>2.75</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J32" s="6">
+        <f>D32-G32</f>
+        <v>3.24</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L32" s="6">
+        <f>IF(K32="Amazon",D32,IF(K32="AliExpress",G32,0))</f>
+        <v>2.75</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" s="15" t="s">
-        <v>130</v>
+      <c r="A34" s="14" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="15" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="15" t="s">
-        <v>133</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="15" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:D19">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="D5:D15">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>D5&lt;G5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G19">
-    <cfRule type="expression" dxfId="0" priority="2">
+  <conditionalFormatting sqref="D29:D32">
+    <cfRule type="expression" dxfId="7" priority="7">
+      <formula>D29&lt;G29</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G15">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>G5&lt;D5</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G29:G32">
+    <cfRule type="expression" dxfId="5" priority="8">
+      <formula>G29&lt;D29</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K5:K19 K23" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K5:K15 K19 K29:K32" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Amazon,AliExpress,None"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1944,24 +2100,671 @@
     <hyperlink ref="F14" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
     <hyperlink ref="C15" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
     <hyperlink ref="F15" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="C16" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="F16" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="C17" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="F17" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="C18" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="F18" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="C19" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="F19" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="C23" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="F23" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="A27" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="A28" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="A29" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="A30" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="A31" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="C19" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="F19" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="A23" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="A24" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="A25" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="A26" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="A27" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="A28" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="C29" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="F29" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="C30" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="F30" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="C31" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="F31" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="C32" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="F32" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
-  <legacyDrawing r:id="rId38"/>
+  <legacyDrawing r:id="rId39"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M37"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="5" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17">
+        <f>D20</f>
+        <v>58.55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+    </row>
+    <row r="4" spans="1:13" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4.75</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2.41</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2.34</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="5">
+        <v>11.49</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="5">
+        <v>3.14</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1.48</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="5">
+        <v>7.99</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2.86</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="5">
+        <v>5.91</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="5">
+        <v>3.32</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="5">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="5">
+        <v>3.12</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10">
+        <f>SUM(D5:D17)</f>
+        <v>56.36</v>
+      </c>
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10">
+        <f>D18+SUM(D19:D19)</f>
+        <v>58.55</v>
+      </c>
+      <c r="E20" s="9"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="19">
+        <v>2.82</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="5">
+        <v>19.95</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="5">
+        <v>11.95</v>
+      </c>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="5">
+        <v>9.99</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="5">
+        <v>6.99</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="5">
+        <v>7.99</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="5">
+        <v>8.99</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" s="5">
+        <v>5.65</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="5">
+        <v>3.99</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="5">
+        <v>5.99</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="5">
+        <v>2.75</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D5:D7 D9:D10">
+    <cfRule type="expression" dxfId="4" priority="8">
+      <formula>D5&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8 D29:D31">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>D8&lt;G8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>D11&lt;G11</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D12:D17">
+    <cfRule type="expression" dxfId="1" priority="4">
+      <formula>D12&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29:G31">
+    <cfRule type="expression" dxfId="0" priority="10">
+      <formula>G29&lt;D29</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="E5:E17 E19 E23 H29:H31" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>"Amazon,AliExpress,None"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="C6" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="C8" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="C9" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="C10" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="C11" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="C12" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="C13" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="C14" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="C15" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="C16" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="C17" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="C19" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="A23" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="C23" r:id="rId16" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
+    <hyperlink ref="A24" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="A25" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="A26" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="A27" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="A28" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="C29" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
+    <hyperlink ref="F29" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
+    <hyperlink ref="C30" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
+    <hyperlink ref="F30" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
+    <hyperlink ref="C31" r:id="rId26" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
+    <hyperlink ref="F31" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
--- a/Sunrise_Clock_Parts.xlsx
+++ b/Sunrise_Clock_Parts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asher\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08BD59C-0B72-4114-B13F-53635DDF17EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12996AC7-117F-4DBA-A487-D5AE3A9028EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6400" yWindow="2250" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -391,6 +391,9 @@
     <t>Same module, with the pull-ups GPIO34/35 need</t>
   </si>
   <si>
+    <t>Gebildet 5 pcs, Flat Head (SS-Momentary-5pcs)</t>
+  </si>
+  <si>
     <t>4.6★, 981 reviews</t>
   </si>
   <si>
@@ -502,10 +505,7 @@
     <t>54,000+ sold</t>
   </si>
   <si>
-    <t>M3 x 5.7 x 4.6</t>
-  </si>
-  <si>
-    <t>Amazon's size is confirmed; on Ali pick M3 × 5.7 × 4.6 if offered</t>
+    <t>Holes are Ø4.0 × 5 mm: a 5 mm insert sits flush. OD 5 mm or wider can split the posts.</t>
   </si>
   <si>
     <t>4.8★, 1,000+ sold</t>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="E1" s="17">
         <f>SUM(G5:G7,G9:G10,G12:G15,D8,D11,G19)</f>
-        <v>51.870000000000005</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -1175,7 +1175,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="5">
-        <v>4.59</v>
+        <v>4.75</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>87</v>
@@ -1185,14 +1185,14 @@
       </c>
       <c r="J5" s="6">
         <f t="shared" ref="J5:J15" si="0">D5-G5</f>
-        <v>7.4</v>
+        <v>7.24</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>11</v>
       </c>
       <c r="L5" s="6">
         <f t="shared" ref="L5:L15" si="1">IF(K5="Amazon",D5,IF(K5="AliExpress",G5,0))</f>
-        <v>4.59</v>
+        <v>4.75</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>89</v>
@@ -1417,25 +1417,25 @@
         <v>2</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="D11" s="5">
         <v>7.99</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G11" s="5">
         <v>4.4000000000000004</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J11" s="6">
         <f t="shared" si="0"/>
@@ -1449,7 +1449,7 @@
         <v>7.99</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
@@ -1460,13 +1460,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" s="5">
         <v>8.9</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>32</v>
@@ -1475,10 +1475,10 @@
         <v>2.86</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J12" s="6">
         <f t="shared" si="0"/>
@@ -1492,7 +1492,7 @@
         <v>2.86</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
@@ -1503,13 +1503,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D13" s="5">
         <v>13.99</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>24</v>
@@ -1518,10 +1518,10 @@
         <v>5.91</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J13" s="6">
         <f t="shared" si="0"/>
@@ -1535,7 +1535,7 @@
         <v>5.91</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -1546,13 +1546,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D14" s="5">
         <v>3.99</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>37</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J14" s="6">
         <f t="shared" si="0"/>
@@ -1576,7 +1576,7 @@
         <v>3.32</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -1587,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D15" s="5">
         <v>13.99</v>
@@ -1602,10 +1602,10 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J15" s="6">
         <f t="shared" si="0"/>
@@ -1619,7 +1619,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -1628,34 +1628,34 @@
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
-      <c r="D16" s="10" t="str">
-        <f ca="1">SUM(D5:D30)</f>
-        <v/>
+      <c r="D16" s="10">
+        <f>SUM(D5:D15,D29:D30)</f>
+        <v>119.56999999999998</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
-      <c r="G16" s="10" t="str">
-        <f ca="1">SUM(G5:G30)</f>
-        <v/>
+      <c r="G16" s="10">
+        <f>SUM(G5:G15,G29:G30)</f>
+        <v>51.149999999999991</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="10" t="str">
-        <f ca="1">SUM(J5:J30)</f>
-        <v/>
+      <c r="J16" s="10">
+        <f>SUM(J5:J15,J29:J30)</f>
+        <v>68.42</v>
       </c>
       <c r="K16" s="9"/>
-      <c r="L16" s="10" t="str">
-        <f ca="1">SUM(L5:L30)</f>
-        <v/>
+      <c r="L16" s="10">
+        <f>SUM(L5:L15,L29:L30)</f>
+        <v>58.89</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
@@ -1666,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D19" s="5">
         <v>7.49</v>
@@ -1681,10 +1681,10 @@
         <v>2.19</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J19" s="6">
         <f>D19-G19</f>
@@ -1698,7 +1698,7 @@
         <v>2.19</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -1707,26 +1707,26 @@
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
-      <c r="D20" s="10" t="str">
-        <f ca="1">D16+SUM(D19:D19)</f>
-        <v/>
+      <c r="D20" s="10">
+        <f>D16+SUM(D19:D19)</f>
+        <v>127.05999999999997</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
-      <c r="G20" s="10" t="str">
-        <f ca="1">G16+SUM(G19:G19)</f>
-        <v/>
+      <c r="G20" s="10">
+        <f>G16+SUM(G19:G19)</f>
+        <v>53.339999999999989</v>
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="10" t="str">
-        <f ca="1">J16+SUM(J19:J19)</f>
-        <v/>
+      <c r="J20" s="10">
+        <f>J16+SUM(J19:J19)</f>
+        <v>73.72</v>
       </c>
       <c r="K20" s="9"/>
-      <c r="L20" s="10" t="str">
-        <f ca="1">L16+SUM(L19:L19)</f>
-        <v/>
+      <c r="L20" s="10">
+        <f>L16+SUM(L19:L19)</f>
+        <v>61.08</v>
       </c>
       <c r="M20" s="9"/>
     </row>
@@ -1737,7 +1737,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
@@ -1758,7 +1758,7 @@
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
       <c r="M24" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -1779,7 +1779,7 @@
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
       <c r="M25" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -1802,7 +1802,7 @@
       <c r="K26" s="13"/>
       <c r="L26" s="13"/>
       <c r="M26" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
@@ -1825,7 +1825,7 @@
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
       <c r="M27" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -1848,10 +1848,10 @@
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
       <c r="M28" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>41</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D29" s="5">
         <v>5.99</v>
@@ -1871,24 +1871,24 @@
         <v>42</v>
       </c>
       <c r="G29" s="5">
-        <v>2.71</v>
+        <v>3.4</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="J29" s="6">
         <f>D29-G29</f>
-        <v>3.2800000000000002</v>
+        <v>2.5900000000000003</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>11</v>
       </c>
       <c r="L29" s="6">
         <f>IF(K29="Amazon",D29,IF(K29="AliExpress",G29,0))</f>
-        <v>2.71</v>
+        <v>3.4</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>147</v>
@@ -1934,7 +1934,7 @@
         <v>5.65</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
